--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="594">
   <si>
     <t>code</t>
   </si>
@@ -34,6 +34,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>Andorran Peseta</t>
+  </si>
+  <si>
+    <t>withdrawn</t>
+  </si>
+  <si>
     <t>AED</t>
   </si>
   <si>
@@ -43,10 +52,19 @@
     <t>active</t>
   </si>
   <si>
+    <t>AFA</t>
+  </si>
+  <si>
+    <t>Afghani</t>
+  </si>
+  <si>
     <t>AFN</t>
   </si>
   <si>
-    <t>Afghani</t>
+    <t>ALK</t>
+  </si>
+  <si>
+    <t>Old Lek</t>
   </si>
   <si>
     <t>ALL</t>
@@ -64,7 +82,7 @@
     <t>ANG</t>
   </si>
   <si>
-    <t>Netherlands Antillian Guilder</t>
+    <t>Netherlands Antillean Guilder</t>
   </si>
   <si>
     <t>AOA</t>
@@ -73,12 +91,51 @@
     <t>Kwanza</t>
   </si>
   <si>
+    <t>AOK</t>
+  </si>
+  <si>
+    <t>AON</t>
+  </si>
+  <si>
+    <t>New Kwanza</t>
+  </si>
+  <si>
+    <t>AOR</t>
+  </si>
+  <si>
+    <t>Kwanza Reajustado</t>
+  </si>
+  <si>
+    <t>ARA</t>
+  </si>
+  <si>
+    <t>Austral</t>
+  </si>
+  <si>
+    <t>ARP</t>
+  </si>
+  <si>
+    <t>Peso Argentino</t>
+  </si>
+  <si>
     <t>ARS</t>
   </si>
   <si>
     <t>Argentine Peso</t>
   </si>
   <si>
+    <t>ARY</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
+    <t>ATS</t>
+  </si>
+  <si>
+    <t>Schilling</t>
+  </si>
+  <si>
     <t>AUD</t>
   </si>
   <si>
@@ -88,19 +145,34 @@
     <t>AWG</t>
   </si>
   <si>
-    <t>Aruban Guilder</t>
+    <t>Aruban Florin</t>
+  </si>
+  <si>
+    <t>AYM</t>
+  </si>
+  <si>
+    <t>Azerbaijan Manat</t>
+  </si>
+  <si>
+    <t>AZM</t>
+  </si>
+  <si>
+    <t>Azerbaijanian Manat</t>
   </si>
   <si>
     <t>AZN</t>
   </si>
   <si>
-    <t>Azerbaijanian Manat</t>
+    <t>BAD</t>
+  </si>
+  <si>
+    <t>Dinar</t>
   </si>
   <si>
     <t>BAM</t>
   </si>
   <si>
-    <t>Convertible Marks</t>
+    <t>Convertible Mark</t>
   </si>
   <si>
     <t>BBD</t>
@@ -115,6 +187,42 @@
     <t>Taka</t>
   </si>
   <si>
+    <t>BEC</t>
+  </si>
+  <si>
+    <t>Convertible Franc</t>
+  </si>
+  <si>
+    <t>BEF</t>
+  </si>
+  <si>
+    <t>Belgian Franc</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>Financial Franc</t>
+  </si>
+  <si>
+    <t>BGJ</t>
+  </si>
+  <si>
+    <t>Lev A/52</t>
+  </si>
+  <si>
+    <t>BGK</t>
+  </si>
+  <si>
+    <t>Lev A/62</t>
+  </si>
+  <si>
+    <t>BGL</t>
+  </si>
+  <si>
+    <t>Lev</t>
+  </si>
+  <si>
     <t>BGN</t>
   </si>
   <si>
@@ -151,18 +259,51 @@
     <t>Boliviano</t>
   </si>
   <si>
+    <t>BOP</t>
+  </si>
+  <si>
+    <t>Peso boliviano</t>
+  </si>
+  <si>
     <t>BOV</t>
   </si>
   <si>
     <t>Mvdol</t>
   </si>
   <si>
+    <t>BRB</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>Cruzado</t>
+  </si>
+  <si>
+    <t>BRE</t>
+  </si>
+  <si>
     <t>BRL</t>
   </si>
   <si>
     <t>Brazilian Real</t>
   </si>
   <si>
+    <t>BRN</t>
+  </si>
+  <si>
+    <t>New Cruzado</t>
+  </si>
+  <si>
+    <t>BRR</t>
+  </si>
+  <si>
+    <t>Cruzeiro Real</t>
+  </si>
+  <si>
     <t>BSD</t>
   </si>
   <si>
@@ -175,27 +316,33 @@
     <t>Ngultrum</t>
   </si>
   <si>
+    <t>BUK</t>
+  </si>
+  <si>
+    <t>Kyat</t>
+  </si>
+  <si>
     <t>BWP</t>
   </si>
   <si>
     <t>Pula</t>
   </si>
   <si>
+    <t>BYB</t>
+  </si>
+  <si>
+    <t>Belarusian Ruble</t>
+  </si>
+  <si>
+    <t>BYN</t>
+  </si>
+  <si>
     <t>BYR</t>
   </si>
   <si>
-    <t>Belarussian Ruble</t>
-  </si>
-  <si>
     <t>Withdrawn from ISO Currency codelist. Use code BYN.</t>
   </si>
   <si>
-    <t>withdrawn</t>
-  </si>
-  <si>
-    <t>BYN</t>
-  </si>
-  <si>
     <t>BZD</t>
   </si>
   <si>
@@ -214,16 +361,34 @@
     <t>Congolese Franc</t>
   </si>
   <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>WIR Franc (for electronic)</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>WIR Euro</t>
+  </si>
+  <si>
     <t>CHF</t>
   </si>
   <si>
     <t>Swiss Franc</t>
   </si>
   <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>WIR Franc</t>
+  </si>
+  <si>
     <t>CLF</t>
   </si>
   <si>
-    <t>Unidades de fomento</t>
+    <t>Unidad de Fomento</t>
   </si>
   <si>
     <t>CLP</t>
@@ -256,6 +421,24 @@
     <t>Costa Rican Colon</t>
   </si>
   <si>
+    <t>CSD</t>
+  </si>
+  <si>
+    <t>Serbian Dinar</t>
+  </si>
+  <si>
+    <t>CSJ</t>
+  </si>
+  <si>
+    <t>Krona A/53</t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
+    <t>Koruna</t>
+  </si>
+  <si>
     <t>CUC</t>
   </si>
   <si>
@@ -271,7 +454,13 @@
     <t>CVE</t>
   </si>
   <si>
-    <t>Cape Verde Escudo</t>
+    <t>Cabo Verde Escudo</t>
+  </si>
+  <si>
+    <t>CYP</t>
+  </si>
+  <si>
+    <t>Cyprus Pound</t>
   </si>
   <si>
     <t>CZK</t>
@@ -280,6 +469,18 @@
     <t>Czech Koruna</t>
   </si>
   <si>
+    <t>DDM</t>
+  </si>
+  <si>
+    <t>Mark der DDR</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>Deutsche Mark</t>
+  </si>
+  <si>
     <t>DJF</t>
   </si>
   <si>
@@ -304,6 +505,18 @@
     <t>Algerian Dinar</t>
   </si>
   <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>Sucre</t>
+  </si>
+  <si>
+    <t>ECV</t>
+  </si>
+  <si>
+    <t>Unidad de Valor Constante (UVC)</t>
+  </si>
+  <si>
     <t>EEK</t>
   </si>
   <si>
@@ -325,6 +538,21 @@
     <t>Nakfa</t>
   </si>
   <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>Spanish Peseta</t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>"A" Account (convertible Peseta Account)</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
     <t>ETB</t>
   </si>
   <si>
@@ -337,6 +565,12 @@
     <t>Euro</t>
   </si>
   <si>
+    <t>FIM</t>
+  </si>
+  <si>
+    <t>Markka</t>
+  </si>
+  <si>
     <t>FJD</t>
   </si>
   <si>
@@ -349,24 +583,45 @@
     <t>Falkland Islands Pound</t>
   </si>
   <si>
+    <t>FRF</t>
+  </si>
+  <si>
+    <t>French Franc</t>
+  </si>
+  <si>
     <t>GBP</t>
   </si>
   <si>
     <t>Pound Sterling</t>
   </si>
   <si>
+    <t>GEK</t>
+  </si>
+  <si>
+    <t>Georgian Coupon</t>
+  </si>
+  <si>
     <t>GEL</t>
   </si>
   <si>
     <t>Lari</t>
   </si>
   <si>
+    <t>GHC</t>
+  </si>
+  <si>
+    <t>Cedi</t>
+  </si>
+  <si>
+    <t>GHP</t>
+  </si>
+  <si>
+    <t>Ghana Cedi</t>
+  </si>
+  <si>
     <t>GHS</t>
   </si>
   <si>
-    <t>Cedi</t>
-  </si>
-  <si>
     <t>GIP</t>
   </si>
   <si>
@@ -379,10 +634,31 @@
     <t>Dalasi</t>
   </si>
   <si>
+    <t>GNE</t>
+  </si>
+  <si>
+    <t>Syli</t>
+  </si>
+  <si>
     <t>GNF</t>
   </si>
   <si>
-    <t>Guinea Franc</t>
+    <t>Guinean Franc</t>
+  </si>
+  <si>
+    <t>GNS</t>
+  </si>
+  <si>
+    <t>GQE</t>
+  </si>
+  <si>
+    <t>Ekwele</t>
+  </si>
+  <si>
+    <t>GRD</t>
+  </si>
+  <si>
+    <t>Drachma</t>
   </si>
   <si>
     <t>GTQ</t>
@@ -391,6 +667,18 @@
     <t>Quetzal</t>
   </si>
   <si>
+    <t>GWE</t>
+  </si>
+  <si>
+    <t>Guinea Escudo</t>
+  </si>
+  <si>
+    <t>GWP</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau Peso</t>
+  </si>
+  <si>
     <t>GYD</t>
   </si>
   <si>
@@ -409,10 +697,16 @@
     <t>Lempira</t>
   </si>
   <si>
+    <t>HRD</t>
+  </si>
+  <si>
+    <t>Croatian Dinar</t>
+  </si>
+  <si>
     <t>HRK</t>
   </si>
   <si>
-    <t>Kuna</t>
+    <t>Croatian Kuna</t>
   </si>
   <si>
     <t>HTG</t>
@@ -433,6 +727,24 @@
     <t>Rupiah</t>
   </si>
   <si>
+    <t>IEP</t>
+  </si>
+  <si>
+    <t>Irish Pound</t>
+  </si>
+  <si>
+    <t>ILP</t>
+  </si>
+  <si>
+    <t>Pound</t>
+  </si>
+  <si>
+    <t>ILR</t>
+  </si>
+  <si>
+    <t>Old Shekel</t>
+  </si>
+  <si>
     <t>ILS</t>
   </si>
   <si>
@@ -457,12 +769,24 @@
     <t>Iranian Rial</t>
   </si>
   <si>
+    <t>ISJ</t>
+  </si>
+  <si>
+    <t>Old Krona</t>
+  </si>
+  <si>
     <t>ISK</t>
   </si>
   <si>
     <t>Iceland Krona</t>
   </si>
   <si>
+    <t>ITL</t>
+  </si>
+  <si>
+    <t>Italian Lira</t>
+  </si>
+  <si>
     <t>JMD</t>
   </si>
   <si>
@@ -502,7 +826,7 @@
     <t>KMF</t>
   </si>
   <si>
-    <t>Comoro Franc</t>
+    <t>Comorian Franc</t>
   </si>
   <si>
     <t>KPW</t>
@@ -535,10 +859,16 @@
     <t>Tenge</t>
   </si>
   <si>
+    <t>LAJ</t>
+  </si>
+  <si>
+    <t>Pathet Lao Kip</t>
+  </si>
+  <si>
     <t>LAK</t>
   </si>
   <si>
-    <t>Kip</t>
+    <t>Lao Kip</t>
   </si>
   <si>
     <t>LBP</t>
@@ -565,18 +895,51 @@
     <t>Loti</t>
   </si>
   <si>
+    <t>LSM</t>
+  </si>
+  <si>
     <t>LTL</t>
   </si>
   <si>
     <t>Lithuanian Litas</t>
   </si>
   <si>
+    <t>LTT</t>
+  </si>
+  <si>
+    <t>Talonas</t>
+  </si>
+  <si>
+    <t>LUC</t>
+  </si>
+  <si>
+    <t>Luxembourg Convertible Franc</t>
+  </si>
+  <si>
+    <t>LUF</t>
+  </si>
+  <si>
+    <t>Luxembourg Franc</t>
+  </si>
+  <si>
+    <t>LUL</t>
+  </si>
+  <si>
+    <t>Luxembourg Financial Franc</t>
+  </si>
+  <si>
     <t>LVL</t>
   </si>
   <si>
     <t>Latvian Lats</t>
   </si>
   <si>
+    <t>LVR</t>
+  </si>
+  <si>
+    <t>Latvian Ruble</t>
+  </si>
+  <si>
     <t>LYD</t>
   </si>
   <si>
@@ -601,18 +964,27 @@
     <t>Malagasy Ariary</t>
   </si>
   <si>
+    <t>MGF</t>
+  </si>
+  <si>
+    <t>Malagasy Franc</t>
+  </si>
+  <si>
     <t>MKD</t>
   </si>
   <si>
     <t>Denar</t>
   </si>
   <si>
+    <t>MLF</t>
+  </si>
+  <si>
+    <t>Mali Franc</t>
+  </si>
+  <si>
     <t>MMK</t>
   </si>
   <si>
-    <t>Kyat</t>
-  </si>
-  <si>
     <t>MNT</t>
   </si>
   <si>
@@ -637,12 +1009,30 @@
     <t>MRU</t>
   </si>
   <si>
+    <t>MTL</t>
+  </si>
+  <si>
+    <t>Maltese Lira</t>
+  </si>
+  <si>
+    <t>MTP</t>
+  </si>
+  <si>
+    <t>Maltese Pound</t>
+  </si>
+  <si>
     <t>MUR</t>
   </si>
   <si>
     <t>Mauritius Rupee</t>
   </si>
   <si>
+    <t>MVQ</t>
+  </si>
+  <si>
+    <t>Maldive Rupee</t>
+  </si>
+  <si>
     <t>MVR</t>
   </si>
   <si>
@@ -652,7 +1042,7 @@
     <t>MWK</t>
   </si>
   <si>
-    <t>Malawi Kwacha</t>
+    <t>Kwacha</t>
   </si>
   <si>
     <t>MXN</t>
@@ -661,6 +1051,9 @@
     <t>Mexican Peso</t>
   </si>
   <si>
+    <t>MXP</t>
+  </si>
+  <si>
     <t>MXV</t>
   </si>
   <si>
@@ -673,12 +1066,21 @@
     <t>Malaysian Ringgit</t>
   </si>
   <si>
+    <t>MZE</t>
+  </si>
+  <si>
+    <t>Mozambique Escudo</t>
+  </si>
+  <si>
+    <t>MZM</t>
+  </si>
+  <si>
+    <t>Mozambique Metical</t>
+  </si>
+  <si>
     <t>MZN</t>
   </si>
   <si>
-    <t>Metical</t>
-  </si>
-  <si>
     <t>NAD</t>
   </si>
   <si>
@@ -691,12 +1093,24 @@
     <t>Naira</t>
   </si>
   <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
     <t>NIO</t>
   </si>
   <si>
     <t>Cordoba Oro</t>
   </si>
   <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>Netherlands Guilder</t>
+  </si>
+  <si>
     <t>NOK</t>
   </si>
   <si>
@@ -727,12 +1141,27 @@
     <t>Balboa</t>
   </si>
   <si>
+    <t>PEH</t>
+  </si>
+  <si>
+    <t>Sol</t>
+  </si>
+  <si>
+    <t>PEI</t>
+  </si>
+  <si>
+    <t>Inti</t>
+  </si>
+  <si>
     <t>PEN</t>
   </si>
   <si>
     <t>Nuevo Sol</t>
   </si>
   <si>
+    <t>PES</t>
+  </si>
+  <si>
     <t>PGK</t>
   </si>
   <si>
@@ -757,6 +1186,15 @@
     <t>Zloty</t>
   </si>
   <si>
+    <t>PLZ</t>
+  </si>
+  <si>
+    <t>PTE</t>
+  </si>
+  <si>
+    <t>Portuguese Escudo</t>
+  </si>
+  <si>
     <t>PYG</t>
   </si>
   <si>
@@ -769,24 +1207,42 @@
     <t>Qatari Rial</t>
   </si>
   <si>
+    <t>RHD</t>
+  </si>
+  <si>
+    <t>Rhodesian Dollar</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>Leu A/52</t>
+  </si>
+  <si>
+    <t>ROL</t>
+  </si>
+  <si>
+    <t>Old Leu</t>
+  </si>
+  <si>
     <t>RON</t>
   </si>
   <si>
-    <t>Romanian Leu</t>
+    <t>New Romanian Leu</t>
   </si>
   <si>
     <t>RSD</t>
   </si>
   <si>
-    <t>Serbian Dinar</t>
-  </si>
-  <si>
     <t>RUB</t>
   </si>
   <si>
     <t>Russian Ruble</t>
   </si>
   <si>
+    <t>RUR</t>
+  </si>
+  <si>
     <t>RWF</t>
   </si>
   <si>
@@ -811,12 +1267,21 @@
     <t>Seychelles Rupee</t>
   </si>
   <si>
+    <t>SDD</t>
+  </si>
+  <si>
+    <t>Sudanese Dinar</t>
+  </si>
+  <si>
     <t>SDG</t>
   </si>
   <si>
     <t>Sudanese Pound</t>
   </si>
   <si>
+    <t>SDP</t>
+  </si>
+  <si>
     <t>SEK</t>
   </si>
   <si>
@@ -835,6 +1300,18 @@
     <t>Saint Helena Pound</t>
   </si>
   <si>
+    <t>SIT</t>
+  </si>
+  <si>
+    <t>Tolar</t>
+  </si>
+  <si>
+    <t>SKK</t>
+  </si>
+  <si>
+    <t>Slovak Koruna</t>
+  </si>
+  <si>
     <t>SLL</t>
   </si>
   <si>
@@ -847,18 +1324,24 @@
     <t>Somali Shilling</t>
   </si>
   <si>
+    <t>SRD</t>
+  </si>
+  <si>
+    <t>Surinam Dollar</t>
+  </si>
+  <si>
+    <t>SRG</t>
+  </si>
+  <si>
+    <t>Surinam Guilder</t>
+  </si>
+  <si>
     <t>SSP</t>
   </si>
   <si>
     <t>South Sudanese Pound</t>
   </si>
   <si>
-    <t>SRD</t>
-  </si>
-  <si>
-    <t>Surinam Dollar</t>
-  </si>
-  <si>
     <t>STD</t>
   </si>
   <si>
@@ -871,6 +1354,12 @@
     <t>STN</t>
   </si>
   <si>
+    <t>SUR</t>
+  </si>
+  <si>
+    <t>Rouble</t>
+  </si>
+  <si>
     <t>SVC</t>
   </si>
   <si>
@@ -895,16 +1384,28 @@
     <t>Baht</t>
   </si>
   <si>
+    <t>TJR</t>
+  </si>
+  <si>
+    <t>Tajik Ruble</t>
+  </si>
+  <si>
     <t>TJS</t>
   </si>
   <si>
     <t>Somoni</t>
   </si>
   <si>
+    <t>TMM</t>
+  </si>
+  <si>
+    <t>Turkmenistan Manat</t>
+  </si>
+  <si>
     <t>TMT</t>
   </si>
   <si>
-    <t>Manat</t>
+    <t>Turkmenistan New Manat</t>
   </si>
   <si>
     <t>TND</t>
@@ -916,13 +1417,25 @@
     <t>TOP</t>
   </si>
   <si>
-    <t>Paanga</t>
+    <t>Pa’anga</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>Timor Escudo</t>
+  </si>
+  <si>
+    <t>TRL</t>
+  </si>
+  <si>
+    <t>Old Turkish Lira</t>
   </si>
   <si>
     <t>TRY</t>
   </si>
   <si>
-    <t>Turkish Lira</t>
+    <t>New Turkish Lira</t>
   </si>
   <si>
     <t>TTD</t>
@@ -949,12 +1462,27 @@
     <t>Hryvnia</t>
   </si>
   <si>
+    <t>UAK</t>
+  </si>
+  <si>
+    <t>Karbovanet</t>
+  </si>
+  <si>
+    <t>UGS</t>
+  </si>
+  <si>
+    <t>Uganda Shilling</t>
+  </si>
+  <si>
+    <t>UGW</t>
+  </si>
+  <si>
+    <t>Old Shilling</t>
+  </si>
+  <si>
     <t>UGX</t>
   </si>
   <si>
-    <t>Uganda Shilling</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -979,7 +1507,19 @@
     <t>UYI</t>
   </si>
   <si>
-    <t>Uruguay Peso en Unidades Indexadas</t>
+    <t>Uruguay Peso en Unidades Indexadas (UI)</t>
+  </si>
+  <si>
+    <t>UYN</t>
+  </si>
+  <si>
+    <t>Old Uruguay Peso</t>
+  </si>
+  <si>
+    <t>UYP</t>
+  </si>
+  <si>
+    <t>Uruguayan Peso</t>
   </si>
   <si>
     <t>UYU</t>
@@ -988,22 +1528,40 @@
     <t>Peso Uruguayo</t>
   </si>
   <si>
+    <t>UYW</t>
+  </si>
+  <si>
+    <t>Unidad Previsional</t>
+  </si>
+  <si>
     <t>UZS</t>
   </si>
   <si>
     <t>Uzbekistan Sum</t>
   </si>
   <si>
+    <t>VEB</t>
+  </si>
+  <si>
+    <t>Bolivar</t>
+  </si>
+  <si>
     <t>VEF</t>
   </si>
   <si>
-    <t>Bolivar</t>
+    <t>Bolívar</t>
   </si>
   <si>
     <t>VES</t>
   </si>
   <si>
-    <t>Bolivar Soberano</t>
+    <t>Bolívar Soberano</t>
+  </si>
+  <si>
+    <t>VNC</t>
+  </si>
+  <si>
+    <t>Old Dong</t>
   </si>
   <si>
     <t>VND</t>
@@ -1030,6 +1588,42 @@
     <t>CFA Franc BEAC</t>
   </si>
   <si>
+    <t>XAG</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>XAU</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>XBA</t>
+  </si>
+  <si>
+    <t>Bond Markets Unit European Composite Unit (EURCO)</t>
+  </si>
+  <si>
+    <t>XBB</t>
+  </si>
+  <si>
+    <t>Bond Markets Unit European Monetary Unit (E.M.U.-6)</t>
+  </si>
+  <si>
+    <t>XBC</t>
+  </si>
+  <si>
+    <t>Bond Markets Unit European Unit of Account 9 (E.U.A.-9)</t>
+  </si>
+  <si>
+    <t>XBD</t>
+  </si>
+  <si>
+    <t>Bond Markets Unit European Unit of Account 17 (E.U.A.-17)</t>
+  </si>
+  <si>
     <t>XBT</t>
   </si>
   <si>
@@ -1045,7 +1639,25 @@
     <t>XDR</t>
   </si>
   <si>
-    <t>International Monetary Fund (IMF) Special Drawing Right (SDR)</t>
+    <t>SDR (Special Drawing Right)</t>
+  </si>
+  <si>
+    <t>XEU</t>
+  </si>
+  <si>
+    <t>European Currency Unit (E.C.U)</t>
+  </si>
+  <si>
+    <t>XFO</t>
+  </si>
+  <si>
+    <t>Gold-Franc</t>
+  </si>
+  <si>
+    <t>XFU</t>
+  </si>
+  <si>
+    <t>UIC-Franc</t>
   </si>
   <si>
     <t>XOF</t>
@@ -1054,18 +1666,87 @@
     <t>CFA Franc BCEAO</t>
   </si>
   <si>
+    <t>XPD</t>
+  </si>
+  <si>
+    <t>Palladium</t>
+  </si>
+  <si>
     <t>XPF</t>
   </si>
   <si>
     <t>CFP Franc</t>
   </si>
   <si>
+    <t>XPT</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>XRE</t>
+  </si>
+  <si>
+    <t>RINET Funds Code</t>
+  </si>
+  <si>
+    <t>XSU</t>
+  </si>
+  <si>
+    <t>XTS</t>
+  </si>
+  <si>
+    <t>Codes specifically reserved for testing purposes</t>
+  </si>
+  <si>
+    <t>XUA</t>
+  </si>
+  <si>
+    <t>ADB Unit of Account</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>The codes assigned for transactions where no currency is involved</t>
+  </si>
+  <si>
+    <t>YDD</t>
+  </si>
+  <si>
+    <t>Yemeni Dinar</t>
+  </si>
+  <si>
     <t>YER</t>
   </si>
   <si>
     <t>Yemeni Rial</t>
   </si>
   <si>
+    <t>YUD</t>
+  </si>
+  <si>
+    <t>New Yugoslavian Dinar</t>
+  </si>
+  <si>
+    <t>YUM</t>
+  </si>
+  <si>
+    <t>New Dinar</t>
+  </si>
+  <si>
+    <t>YUN</t>
+  </si>
+  <si>
+    <t>Yugoslavian Dinar</t>
+  </si>
+  <si>
+    <t>ZAL</t>
+  </si>
+  <si>
+    <t>Financial Rand</t>
+  </si>
+  <si>
     <t>ZAR</t>
   </si>
   <si>
@@ -1084,10 +1765,37 @@
     <t>ZMW</t>
   </si>
   <si>
+    <t>ZRN</t>
+  </si>
+  <si>
+    <t>New Zaire</t>
+  </si>
+  <si>
+    <t>ZRZ</t>
+  </si>
+  <si>
+    <t>Zaire</t>
+  </si>
+  <si>
+    <t>ZWC</t>
+  </si>
+  <si>
+    <t>ZWD</t>
+  </si>
+  <si>
+    <t>Zimbabwe Dollar</t>
+  </si>
+  <si>
     <t>ZWL</t>
   </si>
   <si>
-    <t>Zimbabwe Dollar</t>
+    <t>ZWN</t>
+  </si>
+  <si>
+    <t>Zimbabwe Dollar (new)</t>
+  </si>
+  <si>
+    <t>ZWR</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1461,15 +2169,15 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -1477,13 +2185,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1505,7 +2213,7 @@
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1516,7 +2224,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1538,7 +2246,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1546,7 +2254,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1554,10 +2262,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1565,10 +2273,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -1576,10 +2284,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -1587,10 +2295,10 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
@@ -1598,21 +2306,21 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1620,10 +2328,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -1631,32 +2339,32 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
         <v>41</v>
       </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -1664,10 +2372,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>47</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -1675,21 +2383,21 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -1697,46 +2405,43 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
         <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
@@ -1744,10 +2449,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
         <v>8</v>
@@ -1755,10 +2460,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -1766,10 +2471,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s">
         <v>8</v>
@@ -1777,10 +2482,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
@@ -1788,10 +2493,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F33" t="s">
         <v>8</v>
@@ -1799,76 +2504,76 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
         <v>8</v>
@@ -1876,21 +2581,21 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
         <v>8</v>
@@ -1898,10 +2603,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -1909,10 +2614,10 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
         <v>8</v>
@@ -1920,35 +2625,32 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F47" t="s">
         <v>8</v>
@@ -1956,32 +2658,32 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F50" t="s">
         <v>8</v>
@@ -1989,21 +2691,21 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F52" t="s">
         <v>8</v>
@@ -2011,21 +2713,24 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>105</v>
+      </c>
+      <c r="C54" t="s">
+        <v>108</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -2033,43 +2738,43 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
         <v>8</v>
@@ -2077,109 +2782,109 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
@@ -2187,10 +2892,10 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -2198,10 +2903,10 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F70" t="s">
         <v>8</v>
@@ -2209,43 +2914,43 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F74" t="s">
         <v>8</v>
@@ -2253,21 +2958,21 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F75" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F76" t="s">
         <v>8</v>
@@ -2275,10 +2980,10 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F77" t="s">
         <v>8</v>
@@ -2286,54 +2991,54 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F81" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
         <v>8</v>
@@ -2341,10 +3046,10 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -2352,10 +3057,13 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="C84" t="s">
+        <v>169</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -2363,32 +3071,32 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F85" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F86" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
         <v>8</v>
@@ -2396,10 +3104,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F88" t="s">
         <v>8</v>
@@ -2407,38 +3115,32 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
-      </c>
-      <c r="C90" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
@@ -2446,10 +3148,10 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F92" t="s">
         <v>8</v>
@@ -2457,32 +3159,32 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
         <v>8</v>
@@ -2490,21 +3192,21 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F97" t="s">
         <v>8</v>
@@ -2512,35 +3214,32 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>204</v>
-      </c>
-      <c r="C99" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F99" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F100" t="s">
         <v>8</v>
@@ -2548,43 +3247,43 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B102" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B104" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F104" t="s">
         <v>8</v>
@@ -2592,21 +3291,21 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B105" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B106" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F106" t="s">
         <v>8</v>
@@ -2614,10 +3313,10 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B107" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F107" t="s">
         <v>8</v>
@@ -2625,10 +3324,10 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
         <v>8</v>
@@ -2636,21 +3335,21 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B109" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B110" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F110" t="s">
         <v>8</v>
@@ -2658,10 +3357,10 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B111" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
         <v>8</v>
@@ -2669,43 +3368,43 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B112" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F112" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B113" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F113" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B114" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F114" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B115" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F115" t="s">
         <v>8</v>
@@ -2713,10 +3412,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B116" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F116" t="s">
         <v>8</v>
@@ -2724,32 +3423,32 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B117" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F117" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B118" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B119" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
         <v>8</v>
@@ -2757,10 +3456,10 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B120" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F120" t="s">
         <v>8</v>
@@ -2768,10 +3467,10 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B121" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F121" t="s">
         <v>8</v>
@@ -2779,10 +3478,10 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B122" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="F122" t="s">
         <v>8</v>
@@ -2790,54 +3489,54 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B123" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F123" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F124" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B125" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F125" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B126" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F126" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B127" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F127" t="s">
         <v>8</v>
@@ -2845,21 +3544,21 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B128" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F128" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F129" t="s">
         <v>8</v>
@@ -2867,145 +3566,142 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B130" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F130" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F131" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B132" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F132" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F133" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B134" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F134" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B135" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B136" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F136" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B137" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="F137" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>282</v>
-      </c>
-      <c r="C138" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F139" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F140" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B141" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F141" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -3013,65 +3709,65 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F143" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B144" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F144" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B145" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F145" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F146" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B147" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F147" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="F148" t="s">
         <v>8</v>
@@ -3079,10 +3775,13 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B149" t="s">
-        <v>304</v>
+        <v>295</v>
+      </c>
+      <c r="C149" t="s">
+        <v>169</v>
       </c>
       <c r="F149" t="s">
         <v>8</v>
@@ -3090,10 +3789,10 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B150" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F150" t="s">
         <v>8</v>
@@ -3101,10 +3800,10 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B151" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F151" t="s">
         <v>8</v>
@@ -3112,10 +3811,10 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F152" t="s">
         <v>8</v>
@@ -3123,10 +3822,10 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B153" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F153" t="s">
         <v>8</v>
@@ -3134,10 +3833,13 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B154" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="C154" t="s">
+        <v>169</v>
       </c>
       <c r="F154" t="s">
         <v>8</v>
@@ -3145,10 +3847,10 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F155" t="s">
         <v>8</v>
@@ -3156,79 +3858,76 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>318</v>
-      </c>
-      <c r="C156" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="F156" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="F157" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F158" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B159" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F159" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B160" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="F160" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F161" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
@@ -3236,43 +3935,46 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B163" t="s">
-        <v>333</v>
+        <v>101</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="F164" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="F165" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>339</v>
+        <v>328</v>
+      </c>
+      <c r="C166" t="s">
+        <v>329</v>
       </c>
       <c r="F166" t="s">
         <v>8</v>
@@ -3280,21 +3982,21 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F167" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="F168" t="s">
         <v>8</v>
@@ -3302,10 +4004,10 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B169" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="F169" t="s">
         <v>8</v>
@@ -3313,21 +4015,21 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="F170" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="F171" t="s">
         <v>8</v>
@@ -3335,48 +4037,1473 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="F172" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B173" t="s">
-        <v>353</v>
-      </c>
-      <c r="C173" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="F173" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B174" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F174" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
+        <v>345</v>
+      </c>
+      <c r="B175" t="s">
+        <v>344</v>
+      </c>
+      <c r="F175" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>346</v>
+      </c>
+      <c r="B176" t="s">
+        <v>347</v>
+      </c>
+      <c r="F176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>348</v>
+      </c>
+      <c r="B177" t="s">
+        <v>349</v>
+      </c>
+      <c r="F177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>350</v>
+      </c>
+      <c r="B178" t="s">
+        <v>351</v>
+      </c>
+      <c r="F178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>352</v>
+      </c>
+      <c r="B179" t="s">
+        <v>353</v>
+      </c>
+      <c r="F179" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>354</v>
+      </c>
+      <c r="B180" t="s">
+        <v>353</v>
+      </c>
+      <c r="F180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>355</v>
+      </c>
+      <c r="B181" t="s">
         <v>356</v>
       </c>
-      <c r="B175" t="s">
+      <c r="F181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
         <v>357</v>
       </c>
-      <c r="F175" t="s">
+      <c r="B182" t="s">
+        <v>358</v>
+      </c>
+      <c r="F182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>359</v>
+      </c>
+      <c r="B183" t="s">
+        <v>360</v>
+      </c>
+      <c r="F183" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>361</v>
+      </c>
+      <c r="B184" t="s">
+        <v>362</v>
+      </c>
+      <c r="F184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>363</v>
+      </c>
+      <c r="B185" t="s">
+        <v>364</v>
+      </c>
+      <c r="F185" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>365</v>
+      </c>
+      <c r="B186" t="s">
+        <v>366</v>
+      </c>
+      <c r="F186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>367</v>
+      </c>
+      <c r="B187" t="s">
+        <v>368</v>
+      </c>
+      <c r="F187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>369</v>
+      </c>
+      <c r="B188" t="s">
+        <v>370</v>
+      </c>
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>371</v>
+      </c>
+      <c r="B189" t="s">
+        <v>372</v>
+      </c>
+      <c r="F189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>373</v>
+      </c>
+      <c r="B190" t="s">
+        <v>374</v>
+      </c>
+      <c r="F190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>375</v>
+      </c>
+      <c r="B191" t="s">
+        <v>376</v>
+      </c>
+      <c r="F191" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>377</v>
+      </c>
+      <c r="B192" t="s">
+        <v>378</v>
+      </c>
+      <c r="F192" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>379</v>
+      </c>
+      <c r="B193" t="s">
+        <v>380</v>
+      </c>
+      <c r="F193" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>381</v>
+      </c>
+      <c r="B194" t="s">
+        <v>376</v>
+      </c>
+      <c r="F194" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>382</v>
+      </c>
+      <c r="B195" t="s">
+        <v>383</v>
+      </c>
+      <c r="F195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>384</v>
+      </c>
+      <c r="B196" t="s">
+        <v>385</v>
+      </c>
+      <c r="F196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>386</v>
+      </c>
+      <c r="B197" t="s">
+        <v>387</v>
+      </c>
+      <c r="F197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>388</v>
+      </c>
+      <c r="B198" t="s">
+        <v>389</v>
+      </c>
+      <c r="F198" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>390</v>
+      </c>
+      <c r="B199" t="s">
+        <v>389</v>
+      </c>
+      <c r="F199" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>391</v>
+      </c>
+      <c r="B200" t="s">
+        <v>392</v>
+      </c>
+      <c r="F200" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>393</v>
+      </c>
+      <c r="B201" t="s">
+        <v>394</v>
+      </c>
+      <c r="F201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>395</v>
+      </c>
+      <c r="B202" t="s">
+        <v>396</v>
+      </c>
+      <c r="F202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>397</v>
+      </c>
+      <c r="B203" t="s">
+        <v>398</v>
+      </c>
+      <c r="F203" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>399</v>
+      </c>
+      <c r="B204" t="s">
+        <v>400</v>
+      </c>
+      <c r="F204" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>401</v>
+      </c>
+      <c r="B205" t="s">
+        <v>402</v>
+      </c>
+      <c r="F205" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>403</v>
+      </c>
+      <c r="B206" t="s">
+        <v>404</v>
+      </c>
+      <c r="F206" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>405</v>
+      </c>
+      <c r="B207" t="s">
+        <v>136</v>
+      </c>
+      <c r="F207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>406</v>
+      </c>
+      <c r="B208" t="s">
+        <v>407</v>
+      </c>
+      <c r="F208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>408</v>
+      </c>
+      <c r="B209" t="s">
+        <v>407</v>
+      </c>
+      <c r="F209" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>409</v>
+      </c>
+      <c r="B210" t="s">
+        <v>410</v>
+      </c>
+      <c r="F210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>411</v>
+      </c>
+      <c r="B211" t="s">
+        <v>412</v>
+      </c>
+      <c r="F211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>413</v>
+      </c>
+      <c r="B212" t="s">
+        <v>414</v>
+      </c>
+      <c r="F212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>415</v>
+      </c>
+      <c r="B213" t="s">
+        <v>416</v>
+      </c>
+      <c r="F213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>417</v>
+      </c>
+      <c r="B214" t="s">
+        <v>418</v>
+      </c>
+      <c r="F214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>419</v>
+      </c>
+      <c r="B215" t="s">
+        <v>420</v>
+      </c>
+      <c r="F215" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>421</v>
+      </c>
+      <c r="B216" t="s">
+        <v>420</v>
+      </c>
+      <c r="F216" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>422</v>
+      </c>
+      <c r="B217" t="s">
+        <v>423</v>
+      </c>
+      <c r="F217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>424</v>
+      </c>
+      <c r="B218" t="s">
+        <v>425</v>
+      </c>
+      <c r="F218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>426</v>
+      </c>
+      <c r="B219" t="s">
+        <v>427</v>
+      </c>
+      <c r="F219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>428</v>
+      </c>
+      <c r="B220" t="s">
+        <v>429</v>
+      </c>
+      <c r="F220" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>430</v>
+      </c>
+      <c r="B221" t="s">
+        <v>431</v>
+      </c>
+      <c r="F221" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>432</v>
+      </c>
+      <c r="B222" t="s">
+        <v>433</v>
+      </c>
+      <c r="F222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>434</v>
+      </c>
+      <c r="B223" t="s">
+        <v>435</v>
+      </c>
+      <c r="F223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>436</v>
+      </c>
+      <c r="B224" t="s">
+        <v>437</v>
+      </c>
+      <c r="F224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>438</v>
+      </c>
+      <c r="B225" t="s">
+        <v>439</v>
+      </c>
+      <c r="F225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>440</v>
+      </c>
+      <c r="B226" t="s">
+        <v>441</v>
+      </c>
+      <c r="F226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>442</v>
+      </c>
+      <c r="B227" t="s">
+        <v>443</v>
+      </c>
+      <c r="C227" t="s">
+        <v>444</v>
+      </c>
+      <c r="F227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>445</v>
+      </c>
+      <c r="B228" t="s">
+        <v>443</v>
+      </c>
+      <c r="F228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>446</v>
+      </c>
+      <c r="B229" t="s">
+        <v>447</v>
+      </c>
+      <c r="F229" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>448</v>
+      </c>
+      <c r="B230" t="s">
+        <v>449</v>
+      </c>
+      <c r="F230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>450</v>
+      </c>
+      <c r="B231" t="s">
+        <v>451</v>
+      </c>
+      <c r="F231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>452</v>
+      </c>
+      <c r="B232" t="s">
+        <v>453</v>
+      </c>
+      <c r="F232" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>454</v>
+      </c>
+      <c r="B233" t="s">
+        <v>455</v>
+      </c>
+      <c r="F233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>456</v>
+      </c>
+      <c r="B234" t="s">
+        <v>457</v>
+      </c>
+      <c r="F234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>458</v>
+      </c>
+      <c r="B235" t="s">
+        <v>459</v>
+      </c>
+      <c r="F235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>460</v>
+      </c>
+      <c r="B236" t="s">
+        <v>461</v>
+      </c>
+      <c r="F236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>462</v>
+      </c>
+      <c r="B237" t="s">
+        <v>463</v>
+      </c>
+      <c r="F237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>464</v>
+      </c>
+      <c r="B238" t="s">
+        <v>465</v>
+      </c>
+      <c r="F238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>466</v>
+      </c>
+      <c r="B239" t="s">
+        <v>467</v>
+      </c>
+      <c r="F239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>468</v>
+      </c>
+      <c r="B240" t="s">
+        <v>469</v>
+      </c>
+      <c r="F240" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>470</v>
+      </c>
+      <c r="B241" t="s">
+        <v>471</v>
+      </c>
+      <c r="F241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>472</v>
+      </c>
+      <c r="B242" t="s">
+        <v>473</v>
+      </c>
+      <c r="F242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>474</v>
+      </c>
+      <c r="B243" t="s">
+        <v>475</v>
+      </c>
+      <c r="F243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>476</v>
+      </c>
+      <c r="B244" t="s">
+        <v>477</v>
+      </c>
+      <c r="F244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>478</v>
+      </c>
+      <c r="B245" t="s">
+        <v>479</v>
+      </c>
+      <c r="F245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>480</v>
+      </c>
+      <c r="B246" t="s">
+        <v>481</v>
+      </c>
+      <c r="F246" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>482</v>
+      </c>
+      <c r="B247" t="s">
+        <v>483</v>
+      </c>
+      <c r="F247" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>484</v>
+      </c>
+      <c r="B248" t="s">
+        <v>485</v>
+      </c>
+      <c r="F248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>486</v>
+      </c>
+      <c r="B249" t="s">
+        <v>487</v>
+      </c>
+      <c r="F249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>488</v>
+      </c>
+      <c r="B250" t="s">
+        <v>485</v>
+      </c>
+      <c r="F250" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>489</v>
+      </c>
+      <c r="B251" t="s">
+        <v>490</v>
+      </c>
+      <c r="F251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>491</v>
+      </c>
+      <c r="B252" t="s">
+        <v>492</v>
+      </c>
+      <c r="F252" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>493</v>
+      </c>
+      <c r="B253" t="s">
+        <v>494</v>
+      </c>
+      <c r="C253" t="s">
+        <v>495</v>
+      </c>
+      <c r="F253" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
+        <v>496</v>
+      </c>
+      <c r="B254" t="s">
+        <v>497</v>
+      </c>
+      <c r="F254" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>498</v>
+      </c>
+      <c r="B255" t="s">
+        <v>499</v>
+      </c>
+      <c r="F255" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>500</v>
+      </c>
+      <c r="B256" t="s">
+        <v>501</v>
+      </c>
+      <c r="F256" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>502</v>
+      </c>
+      <c r="B257" t="s">
+        <v>503</v>
+      </c>
+      <c r="F257" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>504</v>
+      </c>
+      <c r="B258" t="s">
+        <v>505</v>
+      </c>
+      <c r="F258" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>506</v>
+      </c>
+      <c r="B259" t="s">
+        <v>507</v>
+      </c>
+      <c r="F259" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>508</v>
+      </c>
+      <c r="B260" t="s">
+        <v>509</v>
+      </c>
+      <c r="F260" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>510</v>
+      </c>
+      <c r="B261" t="s">
+        <v>511</v>
+      </c>
+      <c r="F261" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>512</v>
+      </c>
+      <c r="B262" t="s">
+        <v>513</v>
+      </c>
+      <c r="F262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>514</v>
+      </c>
+      <c r="B263" t="s">
+        <v>515</v>
+      </c>
+      <c r="F263" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>516</v>
+      </c>
+      <c r="B264" t="s">
+        <v>517</v>
+      </c>
+      <c r="F264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>518</v>
+      </c>
+      <c r="B265" t="s">
+        <v>519</v>
+      </c>
+      <c r="F265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>520</v>
+      </c>
+      <c r="B266" t="s">
+        <v>521</v>
+      </c>
+      <c r="F266" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>522</v>
+      </c>
+      <c r="B267" t="s">
+        <v>523</v>
+      </c>
+      <c r="F267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>524</v>
+      </c>
+      <c r="B268" t="s">
+        <v>525</v>
+      </c>
+      <c r="F268" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>526</v>
+      </c>
+      <c r="B269" t="s">
+        <v>527</v>
+      </c>
+      <c r="F269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>528</v>
+      </c>
+      <c r="B270" t="s">
+        <v>529</v>
+      </c>
+      <c r="F270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>530</v>
+      </c>
+      <c r="B271" t="s">
+        <v>531</v>
+      </c>
+      <c r="F271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>532</v>
+      </c>
+      <c r="B272" t="s">
+        <v>533</v>
+      </c>
+      <c r="F272" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>534</v>
+      </c>
+      <c r="B273" t="s">
+        <v>535</v>
+      </c>
+      <c r="F273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>536</v>
+      </c>
+      <c r="B274" t="s">
+        <v>537</v>
+      </c>
+      <c r="F274" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>538</v>
+      </c>
+      <c r="B275" t="s">
+        <v>539</v>
+      </c>
+      <c r="F275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>540</v>
+      </c>
+      <c r="B276" t="s">
+        <v>541</v>
+      </c>
+      <c r="F276" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>542</v>
+      </c>
+      <c r="B277" t="s">
+        <v>543</v>
+      </c>
+      <c r="F277" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>544</v>
+      </c>
+      <c r="B278" t="s">
+        <v>545</v>
+      </c>
+      <c r="F278" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>546</v>
+      </c>
+      <c r="B279" t="s">
+        <v>547</v>
+      </c>
+      <c r="F279" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>548</v>
+      </c>
+      <c r="B280" t="s">
+        <v>549</v>
+      </c>
+      <c r="F280" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>550</v>
+      </c>
+      <c r="B281" t="s">
+        <v>551</v>
+      </c>
+      <c r="F281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>552</v>
+      </c>
+      <c r="B282" t="s">
+        <v>553</v>
+      </c>
+      <c r="F282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>554</v>
+      </c>
+      <c r="B283" t="s">
+        <v>555</v>
+      </c>
+      <c r="F283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>556</v>
+      </c>
+      <c r="B284" t="s">
+        <v>557</v>
+      </c>
+      <c r="F284" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>558</v>
+      </c>
+      <c r="B285" t="s">
+        <v>164</v>
+      </c>
+      <c r="F285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>559</v>
+      </c>
+      <c r="B286" t="s">
+        <v>560</v>
+      </c>
+      <c r="F286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>561</v>
+      </c>
+      <c r="B287" t="s">
+        <v>562</v>
+      </c>
+      <c r="F287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>563</v>
+      </c>
+      <c r="B288" t="s">
+        <v>564</v>
+      </c>
+      <c r="F288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>565</v>
+      </c>
+      <c r="B289" t="s">
+        <v>566</v>
+      </c>
+      <c r="F289" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>567</v>
+      </c>
+      <c r="B290" t="s">
+        <v>568</v>
+      </c>
+      <c r="F290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>569</v>
+      </c>
+      <c r="B291" t="s">
+        <v>570</v>
+      </c>
+      <c r="F291" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>571</v>
+      </c>
+      <c r="B292" t="s">
+        <v>572</v>
+      </c>
+      <c r="F292" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>573</v>
+      </c>
+      <c r="B293" t="s">
+        <v>574</v>
+      </c>
+      <c r="F293" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>575</v>
+      </c>
+      <c r="B294" t="s">
+        <v>576</v>
+      </c>
+      <c r="F294" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>577</v>
+      </c>
+      <c r="B295" t="s">
+        <v>578</v>
+      </c>
+      <c r="F295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>579</v>
+      </c>
+      <c r="B296" t="s">
+        <v>580</v>
+      </c>
+      <c r="C296" t="s">
+        <v>581</v>
+      </c>
+      <c r="F296" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>582</v>
+      </c>
+      <c r="B297" t="s">
+        <v>580</v>
+      </c>
+      <c r="F297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>583</v>
+      </c>
+      <c r="B298" t="s">
+        <v>584</v>
+      </c>
+      <c r="F298" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>585</v>
+      </c>
+      <c r="B299" t="s">
+        <v>586</v>
+      </c>
+      <c r="F299" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>587</v>
+      </c>
+      <c r="B300" t="s">
+        <v>398</v>
+      </c>
+      <c r="F300" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>588</v>
+      </c>
+      <c r="B301" t="s">
+        <v>589</v>
+      </c>
+      <c r="F301" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>590</v>
+      </c>
+      <c r="B302" t="s">
+        <v>589</v>
+      </c>
+      <c r="F302" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>591</v>
+      </c>
+      <c r="B303" t="s">
+        <v>592</v>
+      </c>
+      <c r="F303" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>593</v>
+      </c>
+      <c r="B304" t="s">
+        <v>589</v>
+      </c>
+      <c r="F304" t="s">
         <v>8</v>
       </c>
     </row>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="606">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,42 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
+  </si>
+  <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>
@@ -2127,10 +2163,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:MC304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:341">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2149,3362 +2185,4367 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="II1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>8</v>
+      </c>
+      <c r="LU1" t="s">
+        <v>9</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>10</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>11</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>12</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>13</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>14</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>15</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="MC1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:341">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:341">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:341">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:341">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:341">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:341">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:341">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:341">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:341">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:341">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:341">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:341">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:341">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:341">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:341">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F59" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F63" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F69" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B77" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F79" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F80" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F82" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F85" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F90" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F92" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F93" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F94" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F96" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F98" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F101" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F102" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F103" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F105" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F106" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F109" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B112" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F112" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B113" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F113" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F114" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B115" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F115" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B116" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F117" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B118" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="F118" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B119" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B120" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F120" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B121" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F121" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B122" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B123" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="F123" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F124" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B125" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F125" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F126" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B127" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F127" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="F128" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B129" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="F129" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B130" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F130" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B131" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="F131" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="F132" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B133" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F133" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F134" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B135" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B136" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F136" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B137" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F137" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B138" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B139" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F139" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B140" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F140" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F141" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F142" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B143" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="F143" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B144" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="F144" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F145" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="F146" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F147" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B148" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F148" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C149" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F149" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F150" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F151" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F152" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F153" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B154" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F154" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="F155" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F156" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F157" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F158" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="F159" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="F160" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="F161" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F162" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B163" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F163" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B164" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F164" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B165" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F165" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B166" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C166" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F166" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F167" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B168" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="F168" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B169" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F169" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B170" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F170" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F171" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B172" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="F172" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B173" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="F173" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B174" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F174" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B175" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F175" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B176" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F176" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F177" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B178" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F178" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B179" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F179" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B180" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F180" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B181" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="F181" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B182" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="F182" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B183" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F183" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B184" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F184" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B185" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F185" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B186" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="F186" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B187" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F187" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B188" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="F188" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B189" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="F189" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B190" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F190" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B191" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="F191" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B192" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="F192" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B193" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F193" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B194" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="F194" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B195" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F195" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B196" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F196" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B197" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F197" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B198" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F198" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B199" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F199" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="F200" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B201" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F201" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B202" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F202" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B203" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F203" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B204" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F204" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B205" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F205" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B206" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F206" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B207" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F207" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B208" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F208" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B209" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F209" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B210" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F210" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B211" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F211" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B212" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F212" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B213" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F213" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B214" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="F214" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B215" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="F215" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B216" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="F216" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B217" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F217" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B218" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="F218" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B219" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F219" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B220" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="F220" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B221" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="F221" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="B222" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="F222" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B223" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F223" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B224" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="F224" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B225" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F225" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B226" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F226" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B227" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C227" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F227" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B228" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F228" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B229" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="F229" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B230" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F230" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F231" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B232" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="F232" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B233" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="F233" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B234" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="F234" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B235" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="F235" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B236" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="F236" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B237" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="F237" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B238" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="F238" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="B239" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="F239" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B240" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="F240" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B241" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="F241" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="B242" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="F242" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B243" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="F243" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B244" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="F244" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B245" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="F245" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B246" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="F246" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B247" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F247" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B248" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="F248" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B249" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="F249" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B250" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="F250" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B251" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="F251" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B252" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="F252" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B253" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C253" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="F253" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B254" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="F254" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B255" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="F255" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B256" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="F256" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B257" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F257" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B258" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F258" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B259" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="F259" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B260" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="F260" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B261" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="F261" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B262" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="F262" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B263" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="F263" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B264" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="F264" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B265" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="F265" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B266" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="F266" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B267" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="F267" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B268" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="F268" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B269" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="F269" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="B270" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F270" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B271" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="F271" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B272" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F272" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B273" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="F273" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="B274" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="F274" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B275" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="F275" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B276" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F276" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B277" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="F277" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B278" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F278" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B279" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="F279" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B280" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="F280" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B281" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="F281" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B282" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="F282" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B283" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F283" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="B284" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="F284" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B285" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F285" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B286" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="F286" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B287" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="F287" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B288" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="F288" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B289" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="F289" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B290" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="F290" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B291" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="F291" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B292" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F292" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B293" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="F293" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B294" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="F294" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B295" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="F295" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B296" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C296" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F296" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="B297" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="F297" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="B298" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="F298" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B299" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="F299" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B300" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F300" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B301" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="F301" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B302" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="F302" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="B303" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="F303" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B304" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="F304" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>ADP</t>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="594">
   <si>
     <t>code</t>
   </si>
@@ -32,42 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
-  </si>
-  <si>
-    <t>budget_alignment_guidance</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>ADP</t>
@@ -2163,10 +2127,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:MC304"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:341">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2185,4367 +2149,3362 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ER1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ID1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="II1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LT1" t="s">
-        <v>8</v>
-      </c>
-      <c r="LU1" t="s">
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="LV1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="LW1" t="s">
-        <v>11</v>
-      </c>
-      <c r="LX1" t="s">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="LY1" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="LZ1" t="s">
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="MA1" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="MB1" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="MC1" t="s">
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:341">
-      <c r="A2" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:341">
-      <c r="A3" t="s">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:341">
-      <c r="A4" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:341">
-      <c r="A5" t="s">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:341">
-      <c r="A6" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:341">
-      <c r="A7" t="s">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:341">
-      <c r="A8" t="s">
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:341">
-      <c r="A9" t="s">
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:341">
-      <c r="A10" t="s">
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:341">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:341">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:341">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:341">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:341">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:341">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F53" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F63" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F65" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F79" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F81" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C84" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F86" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B89" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F90" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F93" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F96" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B101" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F101" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B102" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B104" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B106" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B107" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B109" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B110" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B111" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B112" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F112" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B113" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F113" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F114" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B115" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B116" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B117" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F117" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B118" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B119" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B121" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B122" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F123" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F124" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B125" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F125" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B126" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F126" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B127" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B128" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F128" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B130" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F130" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="F131" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B132" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F133" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B134" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F134" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B135" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F135" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B136" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="F136" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B137" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="F137" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B141" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="F141" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F142" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="F143" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B144" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="F144" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B145" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="F145" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="F146" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B147" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F147" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B148" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F148" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B149" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C149" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B150" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F150" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B151" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F151" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="F152" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B153" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F153" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B154" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="F156" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="F157" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F158" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B159" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="F159" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B160" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="F160" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="F161" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="F162" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B163" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F163" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="F164" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F165" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="F166" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B167" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="F167" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F168" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B169" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="F169" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B170" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="F170" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="F171" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="F172" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B173" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="F173" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B174" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F174" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B175" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F175" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B176" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="F176" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B177" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="F177" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B178" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="F178" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B179" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="F179" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B180" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="F180" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B181" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="F181" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B182" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F182" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B183" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="F183" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B184" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="F184" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B185" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="F185" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B186" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="F186" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="B187" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="F187" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B188" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="F188" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="B189" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F189" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B190" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="F190" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B191" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F191" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B192" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="F192" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B193" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="F193" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F194" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B195" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="F195" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="F196" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B197" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F197" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B198" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F198" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B199" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F199" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B200" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="F200" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B201" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="F201" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B202" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="F202" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B203" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="F203" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="B204" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="F204" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B205" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="F205" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B206" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="F206" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B207" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F207" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B208" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="F208" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B209" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="F209" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B210" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="F210" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B211" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="F211" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B212" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="F212" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B213" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="F213" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B214" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="F214" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B215" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="F215" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="F216" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B217" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F217" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B218" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="F218" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B219" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="F219" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B220" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="F220" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B221" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="F221" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B222" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="F222" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B223" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F223" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B224" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="F224" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="F225" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B226" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F226" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C227" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F227" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="B228" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F228" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B229" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="F229" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="F230" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B231" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="F231" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B232" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F232" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B233" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="F233" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="B234" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="F234" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B235" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F235" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B236" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="F236" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B237" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="F237" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B238" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F238" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B239" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="F239" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B240" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F240" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B241" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="F241" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B242" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="F242" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B243" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="F243" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B244" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="F244" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B245" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F245" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B246" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F246" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B247" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="F247" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="B248" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="F248" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="B249" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="F249" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B250" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="F250" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B251" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="F251" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B252" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="F252" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B253" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C253" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="F253" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="B254" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="F254" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="B255" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="F255" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B256" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="F256" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B257" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="F257" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B258" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="F258" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B259" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="F259" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B260" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="F260" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B261" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="F261" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B262" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="F262" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B263" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F263" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B264" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F264" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B265" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="F265" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B266" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="F266" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B267" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="F267" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B268" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="F268" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B269" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="F269" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B270" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="F270" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B271" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="F271" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B272" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="F272" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B273" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="F273" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B274" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="F274" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B275" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="F275" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="B276" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="F276" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B277" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="F277" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B278" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="F278" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="B279" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="F279" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="B280" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F280" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B281" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="F281" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B282" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="F282" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B283" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="F283" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="B284" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="F284" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B285" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F285" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B286" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="F286" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B287" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="F287" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B288" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="F288" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B289" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="F289" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B290" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="F290" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="B291" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="F291" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="B292" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="F292" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B293" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="F293" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B294" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="F294" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B295" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="F295" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B296" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C296" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="F296" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B297" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F297" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B298" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="F298" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B299" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="F299" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B300" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="F300" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="B301" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="F301" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B302" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="F302" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B303" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="F303" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B304" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="F304" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="592">
   <si>
     <t>code</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -2127,10 +2121,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2143,3368 +2137,3362 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>37</v>
       </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>43</v>
       </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>45</v>
       </c>
-      <c r="F21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
         <v>47</v>
       </c>
-      <c r="F22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="F24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
         <v>53</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
         <v>55</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>57</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>58</v>
       </c>
-      <c r="F28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>60</v>
       </c>
-      <c r="F29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>61</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="F30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>63</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>64</v>
       </c>
-      <c r="F31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>65</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>66</v>
       </c>
-      <c r="F32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>68</v>
       </c>
-      <c r="F33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
         <v>69</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-      <c r="F34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>71</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>72</v>
       </c>
-      <c r="F35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
         <v>73</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="F36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
         <v>75</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>76</v>
       </c>
-      <c r="F37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>77</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="F38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>79</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>80</v>
       </c>
-      <c r="F39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
         <v>81</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>82</v>
       </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
         <v>83</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="F41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
         <v>85</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
         <v>87</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
         <v>88</v>
       </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="B45" t="s">
         <v>89</v>
       </c>
-      <c r="B44" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
         <v>90</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>91</v>
       </c>
-      <c r="F45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
         <v>92</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>93</v>
       </c>
-      <c r="F46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+      <c r="D47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
         <v>94</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>95</v>
       </c>
-      <c r="F47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>96</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>97</v>
       </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>99</v>
       </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
         <v>100</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>101</v>
       </c>
-      <c r="F50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
         <v>102</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>103</v>
       </c>
-      <c r="F51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
         <v>104</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
         <v>105</v>
       </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" t="s">
         <v>106</v>
       </c>
-      <c r="B53" t="s">
-        <v>105</v>
-      </c>
-      <c r="F53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
         <v>107</v>
       </c>
-      <c r="B54" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B55" t="s">
         <v>108</v>
       </c>
-      <c r="F54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
         <v>109</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>110</v>
       </c>
-      <c r="F55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
         <v>111</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>112</v>
       </c>
-      <c r="F56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
         <v>113</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>114</v>
       </c>
-      <c r="F57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+      <c r="D58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
         <v>115</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>116</v>
       </c>
-      <c r="F58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
         <v>117</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>118</v>
       </c>
-      <c r="F59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
         <v>119</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>120</v>
       </c>
-      <c r="F60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
         <v>121</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>122</v>
       </c>
-      <c r="F61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
         <v>123</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>124</v>
       </c>
-      <c r="F62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
         <v>125</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
         <v>126</v>
       </c>
-      <c r="F63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
         <v>127</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>128</v>
       </c>
-      <c r="F64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
         <v>129</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>130</v>
       </c>
-      <c r="F65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
         <v>131</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>132</v>
       </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
         <v>133</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>134</v>
       </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
+      <c r="D68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>135</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>136</v>
       </c>
-      <c r="F68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+      <c r="D69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
         <v>137</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>138</v>
       </c>
-      <c r="F69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+      <c r="D70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
         <v>139</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>140</v>
       </c>
-      <c r="F70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>141</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>142</v>
       </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
         <v>143</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>144</v>
       </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>145</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>146</v>
       </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+      <c r="D74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
         <v>147</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>148</v>
       </c>
-      <c r="F74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
         <v>149</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>150</v>
       </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
+      <c r="D76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
         <v>151</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>152</v>
       </c>
-      <c r="F76" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+      <c r="D77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
         <v>153</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>154</v>
       </c>
-      <c r="F77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
         <v>155</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>156</v>
       </c>
-      <c r="F78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
         <v>157</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>158</v>
       </c>
-      <c r="F79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+      <c r="D80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
         <v>159</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>160</v>
       </c>
-      <c r="F80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
         <v>161</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>162</v>
       </c>
-      <c r="F81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+      <c r="D82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
         <v>163</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>164</v>
       </c>
-      <c r="F82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+      <c r="D83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
         <v>165</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B84" t="s">
         <v>166</v>
       </c>
-      <c r="F83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+      <c r="C84" t="s">
         <v>167</v>
       </c>
-      <c r="B84" t="s">
+      <c r="D84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
         <v>168</v>
       </c>
-      <c r="C84" t="s">
+      <c r="B85" t="s">
         <v>169</v>
       </c>
-      <c r="F84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
         <v>170</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>171</v>
       </c>
-      <c r="F85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
         <v>172</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>173</v>
       </c>
-      <c r="F86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+      <c r="D87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
         <v>174</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="F87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+      <c r="D88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
         <v>176</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
         <v>177</v>
       </c>
-      <c r="F88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
+      <c r="B90" t="s">
         <v>178</v>
       </c>
-      <c r="B89" t="s">
-        <v>175</v>
-      </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
         <v>179</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>180</v>
       </c>
-      <c r="F90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" t="s">
+      <c r="D91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
         <v>181</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>182</v>
       </c>
-      <c r="F91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" t="s">
+      <c r="D92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
         <v>183</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B93" t="s">
         <v>184</v>
       </c>
-      <c r="F92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" t="s">
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
         <v>185</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>186</v>
       </c>
-      <c r="F93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" t="s">
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
         <v>187</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>188</v>
       </c>
-      <c r="F94" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" t="s">
+      <c r="D95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>190</v>
       </c>
-      <c r="F95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>192</v>
       </c>
-      <c r="F96" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" t="s">
+      <c r="D97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
         <v>193</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B98" t="s">
         <v>194</v>
       </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
         <v>195</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>196</v>
       </c>
-      <c r="F98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" t="s">
+      <c r="D99" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
         <v>197</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>198</v>
       </c>
-      <c r="F99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" t="s">
+      <c r="D100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
+        <v>198</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
         <v>200</v>
       </c>
-      <c r="F100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101" t="s">
+      <c r="B102" t="s">
         <v>201</v>
       </c>
-      <c r="B101" t="s">
-        <v>200</v>
-      </c>
-      <c r="F101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
         <v>202</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>203</v>
       </c>
-      <c r="F102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103" t="s">
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
         <v>204</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B104" t="s">
         <v>205</v>
       </c>
-      <c r="F103" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" t="s">
+      <c r="D104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
         <v>206</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B105" t="s">
         <v>207</v>
       </c>
-      <c r="F104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105" t="s">
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
         <v>208</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B106" t="s">
+        <v>205</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
         <v>209</v>
       </c>
-      <c r="F105" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
+      <c r="B107" t="s">
         <v>210</v>
       </c>
-      <c r="B106" t="s">
-        <v>207</v>
-      </c>
-      <c r="F106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107" t="s">
+      <c r="D107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
         <v>211</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B108" t="s">
         <v>212</v>
       </c>
-      <c r="F107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
+      <c r="D108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
         <v>213</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B109" t="s">
         <v>214</v>
       </c>
-      <c r="F108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" t="s">
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
         <v>215</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>216</v>
       </c>
-      <c r="F109" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
+      <c r="D110" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
         <v>217</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B111" t="s">
         <v>218</v>
       </c>
-      <c r="F110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" t="s">
+      <c r="D111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
         <v>219</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B112" t="s">
         <v>220</v>
       </c>
-      <c r="F111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" t="s">
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
         <v>221</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B113" t="s">
         <v>222</v>
       </c>
-      <c r="F112" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
         <v>223</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B114" t="s">
         <v>224</v>
       </c>
-      <c r="F113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
         <v>225</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B115" t="s">
         <v>226</v>
       </c>
-      <c r="F114" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" t="s">
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
         <v>227</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B116" t="s">
         <v>228</v>
       </c>
-      <c r="F115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" t="s">
+      <c r="D116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
         <v>229</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B117" t="s">
         <v>230</v>
       </c>
-      <c r="F116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
         <v>231</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B118" t="s">
         <v>232</v>
       </c>
-      <c r="F117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
         <v>233</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B119" t="s">
         <v>234</v>
       </c>
-      <c r="F118" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" t="s">
+      <c r="D119" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
         <v>235</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B120" t="s">
         <v>236</v>
       </c>
-      <c r="F119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" t="s">
+      <c r="D120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
         <v>237</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>238</v>
       </c>
-      <c r="F120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
+      <c r="D121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
         <v>239</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B122" t="s">
         <v>240</v>
       </c>
-      <c r="F121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
         <v>241</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B123" t="s">
         <v>242</v>
       </c>
-      <c r="F122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" t="s">
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
         <v>243</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B124" t="s">
         <v>244</v>
       </c>
-      <c r="F123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" t="s">
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
         <v>245</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B125" t="s">
         <v>246</v>
       </c>
-      <c r="F124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
         <v>247</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B126" t="s">
         <v>248</v>
       </c>
-      <c r="F125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
         <v>249</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B127" t="s">
         <v>250</v>
       </c>
-      <c r="F126" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
         <v>251</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B128" t="s">
         <v>252</v>
       </c>
-      <c r="F127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
         <v>253</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B129" t="s">
         <v>254</v>
       </c>
-      <c r="F128" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
+      <c r="D129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
         <v>255</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B130" t="s">
         <v>256</v>
       </c>
-      <c r="F129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130" t="s">
+      <c r="D130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
         <v>257</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B131" t="s">
         <v>258</v>
       </c>
-      <c r="F130" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131" t="s">
+      <c r="D131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
         <v>259</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B132" t="s">
         <v>260</v>
       </c>
-      <c r="F131" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132" t="s">
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
         <v>261</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B133" t="s">
         <v>262</v>
       </c>
-      <c r="F132" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
+      <c r="D133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
         <v>263</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B134" t="s">
         <v>264</v>
       </c>
-      <c r="F133" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" t="s">
+      <c r="D134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
         <v>265</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B135" t="s">
         <v>266</v>
       </c>
-      <c r="F134" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" t="s">
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
         <v>267</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B136" t="s">
         <v>268</v>
       </c>
-      <c r="F135" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136" t="s">
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
         <v>269</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B137" t="s">
         <v>270</v>
       </c>
-      <c r="F136" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" t="s">
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
         <v>271</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>272</v>
       </c>
-      <c r="F137" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" t="s">
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
         <v>273</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B139" t="s">
         <v>274</v>
       </c>
-      <c r="F138" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" t="s">
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
         <v>275</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>276</v>
       </c>
-      <c r="F139" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140" t="s">
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
         <v>277</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B141" t="s">
         <v>278</v>
       </c>
-      <c r="F140" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" t="s">
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
         <v>279</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B142" t="s">
         <v>280</v>
       </c>
-      <c r="F141" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" t="s">
+      <c r="D142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
         <v>281</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B143" t="s">
         <v>282</v>
       </c>
-      <c r="F142" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" t="s">
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
         <v>283</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B144" t="s">
         <v>284</v>
       </c>
-      <c r="F143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144" t="s">
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
         <v>285</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B145" t="s">
         <v>286</v>
       </c>
-      <c r="F144" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
+      <c r="D145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
         <v>287</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B146" t="s">
         <v>288</v>
       </c>
-      <c r="F145" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
+      <c r="D146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
         <v>289</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B147" t="s">
         <v>290</v>
       </c>
-      <c r="F146" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
+      <c r="D147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
         <v>291</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B148" t="s">
+        <v>290</v>
+      </c>
+      <c r="D148" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
         <v>292</v>
       </c>
-      <c r="F147" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+      <c r="B149" t="s">
         <v>293</v>
       </c>
-      <c r="B148" t="s">
-        <v>292</v>
-      </c>
-      <c r="F148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
+      <c r="C149" t="s">
+        <v>167</v>
+      </c>
+      <c r="D149" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
         <v>294</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B150" t="s">
         <v>295</v>
       </c>
-      <c r="C149" t="s">
-        <v>169</v>
-      </c>
-      <c r="F149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+      <c r="D150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
         <v>296</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>297</v>
       </c>
-      <c r="F150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
         <v>298</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>299</v>
       </c>
-      <c r="F151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
+      <c r="D152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
         <v>300</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B153" t="s">
         <v>301</v>
       </c>
-      <c r="F152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
+      <c r="D153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
         <v>302</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B154" t="s">
         <v>303</v>
       </c>
-      <c r="F153" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
+      <c r="C154" t="s">
+        <v>167</v>
+      </c>
+      <c r="D154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
         <v>304</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>305</v>
       </c>
-      <c r="C154" t="s">
-        <v>169</v>
-      </c>
-      <c r="F154" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
+      <c r="D155" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
         <v>306</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>307</v>
       </c>
-      <c r="F155" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
         <v>308</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>309</v>
       </c>
-      <c r="F156" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
         <v>310</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>311</v>
       </c>
-      <c r="F157" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
+      <c r="D158" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
         <v>312</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>313</v>
       </c>
-      <c r="F158" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
         <v>314</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B160" t="s">
         <v>315</v>
       </c>
-      <c r="F159" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
+      <c r="D160" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
         <v>316</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>317</v>
       </c>
-      <c r="F160" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
+      <c r="D161" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
         <v>318</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B162" t="s">
         <v>319</v>
       </c>
-      <c r="F161" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" t="s">
+      <c r="D162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
         <v>320</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B163" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
         <v>321</v>
       </c>
-      <c r="F162" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" t="s">
+      <c r="B164" t="s">
         <v>322</v>
       </c>
-      <c r="B163" t="s">
-        <v>101</v>
-      </c>
-      <c r="F163" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" t="s">
+      <c r="D164" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
         <v>323</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B165" t="s">
         <v>324</v>
       </c>
-      <c r="F164" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
         <v>325</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B166" t="s">
         <v>326</v>
       </c>
-      <c r="F165" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166" t="s">
+      <c r="C166" t="s">
         <v>327</v>
       </c>
-      <c r="B166" t="s">
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
         <v>328</v>
       </c>
-      <c r="C166" t="s">
+      <c r="B167" t="s">
+        <v>326</v>
+      </c>
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
         <v>329</v>
       </c>
-      <c r="F166" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" t="s">
+      <c r="B168" t="s">
         <v>330</v>
       </c>
-      <c r="B167" t="s">
-        <v>328</v>
-      </c>
-      <c r="F167" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168" t="s">
+      <c r="D168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
         <v>331</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>332</v>
       </c>
-      <c r="F168" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169" t="s">
+      <c r="D169" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
         <v>333</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B170" t="s">
         <v>334</v>
       </c>
-      <c r="F169" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170" t="s">
+      <c r="D170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
         <v>335</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B171" t="s">
         <v>336</v>
       </c>
-      <c r="F170" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
+      <c r="D171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
         <v>337</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B172" t="s">
         <v>338</v>
       </c>
-      <c r="F171" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172" t="s">
+      <c r="D172" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
         <v>339</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B173" t="s">
         <v>340</v>
       </c>
-      <c r="F172" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173" t="s">
+      <c r="D173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
         <v>341</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B174" t="s">
         <v>342</v>
       </c>
-      <c r="F173" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174" t="s">
+      <c r="D174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
         <v>343</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
+        <v>342</v>
+      </c>
+      <c r="D175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
         <v>344</v>
       </c>
-      <c r="F174" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175" t="s">
+      <c r="B176" t="s">
         <v>345</v>
       </c>
-      <c r="B175" t="s">
-        <v>344</v>
-      </c>
-      <c r="F175" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" t="s">
+      <c r="D176" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
         <v>346</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B177" t="s">
         <v>347</v>
       </c>
-      <c r="F176" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" t="s">
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
         <v>348</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B178" t="s">
         <v>349</v>
       </c>
-      <c r="F177" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178" t="s">
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
         <v>350</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
         <v>351</v>
       </c>
-      <c r="F178" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179" t="s">
+      <c r="D179" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
         <v>352</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B180" t="s">
+        <v>351</v>
+      </c>
+      <c r="D180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
         <v>353</v>
       </c>
-      <c r="F179" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180" t="s">
+      <c r="B181" t="s">
         <v>354</v>
       </c>
-      <c r="B180" t="s">
-        <v>353</v>
-      </c>
-      <c r="F180" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" t="s">
+      <c r="D181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
         <v>355</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B182" t="s">
         <v>356</v>
       </c>
-      <c r="F181" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" t="s">
+      <c r="D182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
         <v>357</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B183" t="s">
         <v>358</v>
       </c>
-      <c r="F182" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183" t="s">
+      <c r="D183" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
         <v>359</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>360</v>
       </c>
-      <c r="F183" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" t="s">
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
         <v>361</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B185" t="s">
         <v>362</v>
       </c>
-      <c r="F184" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" t="s">
+      <c r="D185" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
         <v>363</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B186" t="s">
         <v>364</v>
       </c>
-      <c r="F185" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186" t="s">
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
         <v>365</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B187" t="s">
         <v>366</v>
       </c>
-      <c r="F186" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187" t="s">
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
         <v>367</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B188" t="s">
         <v>368</v>
       </c>
-      <c r="F187" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188" t="s">
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
         <v>369</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B189" t="s">
         <v>370</v>
       </c>
-      <c r="F188" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189" t="s">
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
         <v>371</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>372</v>
       </c>
-      <c r="F189" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" t="s">
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
         <v>373</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B191" t="s">
         <v>374</v>
       </c>
-      <c r="F190" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" t="s">
+      <c r="D191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
         <v>375</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B192" t="s">
         <v>376</v>
       </c>
-      <c r="F191" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" t="s">
+      <c r="D192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
         <v>377</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B193" t="s">
         <v>378</v>
       </c>
-      <c r="F192" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" t="s">
+      <c r="D193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
         <v>379</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
+        <v>374</v>
+      </c>
+      <c r="D194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
         <v>380</v>
       </c>
-      <c r="F193" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
+      <c r="B195" t="s">
         <v>381</v>
       </c>
-      <c r="B194" t="s">
-        <v>376</v>
-      </c>
-      <c r="F194" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" t="s">
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
         <v>382</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B196" t="s">
         <v>383</v>
       </c>
-      <c r="F195" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" t="s">
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
         <v>384</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B197" t="s">
         <v>385</v>
       </c>
-      <c r="F196" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" t="s">
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
         <v>386</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B198" t="s">
         <v>387</v>
       </c>
-      <c r="F197" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" t="s">
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
         <v>388</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
+        <v>387</v>
+      </c>
+      <c r="D199" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
         <v>389</v>
       </c>
-      <c r="F198" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" t="s">
+      <c r="B200" t="s">
         <v>390</v>
       </c>
-      <c r="B199" t="s">
-        <v>389</v>
-      </c>
-      <c r="F199" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" t="s">
+      <c r="D200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
         <v>391</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B201" t="s">
         <v>392</v>
       </c>
-      <c r="F200" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201" t="s">
+      <c r="D201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
         <v>393</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>394</v>
       </c>
-      <c r="F201" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" t="s">
+      <c r="D202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
         <v>395</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B203" t="s">
         <v>396</v>
       </c>
-      <c r="F202" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" t="s">
+      <c r="D203" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
         <v>397</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>398</v>
       </c>
-      <c r="F203" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
+      <c r="D204" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
         <v>399</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>400</v>
       </c>
-      <c r="F204" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" t="s">
+      <c r="D205" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
         <v>401</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B206" t="s">
         <v>402</v>
       </c>
-      <c r="F205" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206" t="s">
+      <c r="D206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
         <v>403</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B207" t="s">
+        <v>134</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
         <v>404</v>
       </c>
-      <c r="F206" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207" t="s">
+      <c r="B208" t="s">
         <v>405</v>
       </c>
-      <c r="B207" t="s">
-        <v>136</v>
-      </c>
-      <c r="F207" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208" t="s">
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
         <v>406</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B209" t="s">
+        <v>405</v>
+      </c>
+      <c r="D209" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
         <v>407</v>
       </c>
-      <c r="F208" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
+      <c r="B210" t="s">
         <v>408</v>
       </c>
-      <c r="B209" t="s">
-        <v>407</v>
-      </c>
-      <c r="F209" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
+      <c r="D210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
         <v>409</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B211" t="s">
         <v>410</v>
       </c>
-      <c r="F210" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
         <v>411</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
         <v>412</v>
       </c>
-      <c r="F211" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
+      <c r="D212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
         <v>413</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B213" t="s">
         <v>414</v>
       </c>
-      <c r="F212" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
+      <c r="D213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
         <v>415</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B214" t="s">
         <v>416</v>
       </c>
-      <c r="F213" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
+      <c r="D214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
         <v>417</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B215" t="s">
         <v>418</v>
       </c>
-      <c r="F214" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215" t="s">
+      <c r="D215" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
         <v>419</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B216" t="s">
+        <v>418</v>
+      </c>
+      <c r="D216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
         <v>420</v>
       </c>
-      <c r="F215" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216" t="s">
+      <c r="B217" t="s">
         <v>421</v>
       </c>
-      <c r="B216" t="s">
-        <v>420</v>
-      </c>
-      <c r="F216" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217" t="s">
+      <c r="D217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
         <v>422</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B218" t="s">
         <v>423</v>
       </c>
-      <c r="F217" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218" t="s">
+      <c r="D218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
         <v>424</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B219" t="s">
         <v>425</v>
       </c>
-      <c r="F218" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219" t="s">
+      <c r="D219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
         <v>426</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B220" t="s">
         <v>427</v>
       </c>
-      <c r="F219" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220" t="s">
+      <c r="D220" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
         <v>428</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B221" t="s">
         <v>429</v>
       </c>
-      <c r="F220" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221" t="s">
+      <c r="D221" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
         <v>430</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B222" t="s">
         <v>431</v>
       </c>
-      <c r="F221" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222" t="s">
+      <c r="D222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
         <v>432</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B223" t="s">
         <v>433</v>
       </c>
-      <c r="F222" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223" t="s">
+      <c r="D223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
         <v>434</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B224" t="s">
         <v>435</v>
       </c>
-      <c r="F223" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224" t="s">
+      <c r="D224" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
         <v>436</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B225" t="s">
         <v>437</v>
       </c>
-      <c r="F224" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225" t="s">
+      <c r="D225" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
         <v>438</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B226" t="s">
         <v>439</v>
       </c>
-      <c r="F225" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226" t="s">
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
         <v>440</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B227" t="s">
         <v>441</v>
       </c>
-      <c r="F226" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227" t="s">
+      <c r="C227" t="s">
         <v>442</v>
       </c>
-      <c r="B227" t="s">
+      <c r="D227" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
         <v>443</v>
       </c>
-      <c r="C227" t="s">
+      <c r="B228" t="s">
+        <v>441</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
         <v>444</v>
       </c>
-      <c r="F227" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228" t="s">
+      <c r="B229" t="s">
         <v>445</v>
       </c>
-      <c r="B228" t="s">
-        <v>443</v>
-      </c>
-      <c r="F228" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229" t="s">
+      <c r="D229" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
         <v>446</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B230" t="s">
         <v>447</v>
       </c>
-      <c r="F229" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230" t="s">
+      <c r="D230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
         <v>448</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B231" t="s">
         <v>449</v>
       </c>
-      <c r="F230" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231" t="s">
+      <c r="D231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
         <v>450</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B232" t="s">
         <v>451</v>
       </c>
-      <c r="F231" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232" t="s">
+      <c r="D232" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
         <v>452</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B233" t="s">
         <v>453</v>
       </c>
-      <c r="F232" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233" t="s">
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
         <v>454</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B234" t="s">
         <v>455</v>
       </c>
-      <c r="F233" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234" t="s">
+      <c r="D234" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
         <v>456</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B235" t="s">
         <v>457</v>
       </c>
-      <c r="F234" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235" t="s">
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
         <v>458</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B236" t="s">
         <v>459</v>
       </c>
-      <c r="F235" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236" t="s">
+      <c r="D236" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
         <v>460</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B237" t="s">
         <v>461</v>
       </c>
-      <c r="F236" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237" t="s">
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
         <v>462</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B238" t="s">
         <v>463</v>
       </c>
-      <c r="F237" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238" t="s">
+      <c r="D238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
         <v>464</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B239" t="s">
         <v>465</v>
       </c>
-      <c r="F238" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239" t="s">
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
         <v>466</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B240" t="s">
         <v>467</v>
       </c>
-      <c r="F239" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240" t="s">
+      <c r="D240" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
         <v>468</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B241" t="s">
         <v>469</v>
       </c>
-      <c r="F240" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241" t="s">
+      <c r="D241" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
         <v>470</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B242" t="s">
         <v>471</v>
       </c>
-      <c r="F241" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242" t="s">
+      <c r="D242" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
         <v>472</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B243" t="s">
         <v>473</v>
       </c>
-      <c r="F242" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243" t="s">
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
         <v>474</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B244" t="s">
         <v>475</v>
       </c>
-      <c r="F243" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244" t="s">
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
         <v>476</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B245" t="s">
         <v>477</v>
       </c>
-      <c r="F244" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245" t="s">
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
         <v>478</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B246" t="s">
         <v>479</v>
       </c>
-      <c r="F245" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246" t="s">
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
         <v>480</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B247" t="s">
         <v>481</v>
       </c>
-      <c r="F246" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247" t="s">
+      <c r="D247" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
         <v>482</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B248" t="s">
         <v>483</v>
       </c>
-      <c r="F247" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248" t="s">
+      <c r="D248" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
         <v>484</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B249" t="s">
         <v>485</v>
       </c>
-      <c r="F248" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249" t="s">
+      <c r="D249" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
         <v>486</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B250" t="s">
+        <v>483</v>
+      </c>
+      <c r="D250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
         <v>487</v>
       </c>
-      <c r="F249" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250" t="s">
+      <c r="B251" t="s">
         <v>488</v>
       </c>
-      <c r="B250" t="s">
-        <v>485</v>
-      </c>
-      <c r="F250" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251" t="s">
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
         <v>489</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B252" t="s">
         <v>490</v>
       </c>
-      <c r="F251" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252" t="s">
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
         <v>491</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B253" t="s">
         <v>492</v>
       </c>
-      <c r="F252" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253" t="s">
+      <c r="C253" t="s">
         <v>493</v>
       </c>
-      <c r="B253" t="s">
+      <c r="D253" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
         <v>494</v>
       </c>
-      <c r="C253" t="s">
+      <c r="B254" t="s">
         <v>495</v>
       </c>
-      <c r="F253" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254" t="s">
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
         <v>496</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B255" t="s">
         <v>497</v>
       </c>
-      <c r="F254" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255" t="s">
+      <c r="D255" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
         <v>498</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B256" t="s">
         <v>499</v>
       </c>
-      <c r="F255" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256" t="s">
+      <c r="D256" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
         <v>500</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B257" t="s">
         <v>501</v>
       </c>
-      <c r="F256" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257" t="s">
+      <c r="D257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
         <v>502</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B258" t="s">
         <v>503</v>
       </c>
-      <c r="F257" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258" t="s">
+      <c r="D258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
         <v>504</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B259" t="s">
         <v>505</v>
       </c>
-      <c r="F258" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259" t="s">
+      <c r="D259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
         <v>506</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B260" t="s">
         <v>507</v>
       </c>
-      <c r="F259" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260" t="s">
+      <c r="D260" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
         <v>508</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B261" t="s">
         <v>509</v>
       </c>
-      <c r="F260" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261" t="s">
+      <c r="D261" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
         <v>510</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B262" t="s">
         <v>511</v>
       </c>
-      <c r="F261" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262" t="s">
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
         <v>512</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B263" t="s">
         <v>513</v>
       </c>
-      <c r="F262" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263" t="s">
+      <c r="D263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
         <v>514</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B264" t="s">
         <v>515</v>
       </c>
-      <c r="F263" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" t="s">
+      <c r="D264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
         <v>516</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B265" t="s">
         <v>517</v>
       </c>
-      <c r="F264" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265" t="s">
+      <c r="D265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
         <v>518</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B266" t="s">
         <v>519</v>
       </c>
-      <c r="F265" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266" t="s">
+      <c r="D266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
         <v>520</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B267" t="s">
         <v>521</v>
       </c>
-      <c r="F266" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267" t="s">
+      <c r="D267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
         <v>522</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B268" t="s">
         <v>523</v>
       </c>
-      <c r="F267" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
-      <c r="A268" t="s">
+      <c r="D268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
         <v>524</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B269" t="s">
         <v>525</v>
       </c>
-      <c r="F268" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269" t="s">
+      <c r="D269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
         <v>526</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B270" t="s">
         <v>527</v>
       </c>
-      <c r="F269" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" t="s">
+      <c r="D270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
         <v>528</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B271" t="s">
         <v>529</v>
       </c>
-      <c r="F270" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271" t="s">
+      <c r="D271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
         <v>530</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B272" t="s">
         <v>531</v>
       </c>
-      <c r="F271" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="A272" t="s">
+      <c r="D272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
         <v>532</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B273" t="s">
         <v>533</v>
       </c>
-      <c r="F272" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273" t="s">
+      <c r="D273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
         <v>534</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B274" t="s">
         <v>535</v>
       </c>
-      <c r="F273" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
-      <c r="A274" t="s">
+      <c r="D274" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
         <v>536</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B275" t="s">
         <v>537</v>
       </c>
-      <c r="F274" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
-      <c r="A275" t="s">
+      <c r="D275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
         <v>538</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B276" t="s">
         <v>539</v>
       </c>
-      <c r="F275" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
-      <c r="A276" t="s">
+      <c r="D276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
         <v>540</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B277" t="s">
         <v>541</v>
       </c>
-      <c r="F276" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
-      <c r="A277" t="s">
+      <c r="D277" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
         <v>542</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B278" t="s">
         <v>543</v>
       </c>
-      <c r="F277" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
-      <c r="A278" t="s">
+      <c r="D278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
         <v>544</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B279" t="s">
         <v>545</v>
       </c>
-      <c r="F278" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
-      <c r="A279" t="s">
+      <c r="D279" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
         <v>546</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B280" t="s">
         <v>547</v>
       </c>
-      <c r="F279" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
-      <c r="A280" t="s">
+      <c r="D280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
         <v>548</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B281" t="s">
         <v>549</v>
       </c>
-      <c r="F280" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
-      <c r="A281" t="s">
+      <c r="D281" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
         <v>550</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B282" t="s">
         <v>551</v>
       </c>
-      <c r="F281" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
-      <c r="A282" t="s">
+      <c r="D282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
         <v>552</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B283" t="s">
         <v>553</v>
       </c>
-      <c r="F282" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
-      <c r="A283" t="s">
+      <c r="D283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
         <v>554</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B284" t="s">
         <v>555</v>
       </c>
-      <c r="F283" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
-      <c r="A284" t="s">
+      <c r="D284" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
         <v>556</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B285" t="s">
+        <v>162</v>
+      </c>
+      <c r="D285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
         <v>557</v>
       </c>
-      <c r="F284" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
-      <c r="A285" t="s">
+      <c r="B286" t="s">
         <v>558</v>
       </c>
-      <c r="B285" t="s">
-        <v>164</v>
-      </c>
-      <c r="F285" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
-      <c r="A286" t="s">
+      <c r="D286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
         <v>559</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B287" t="s">
         <v>560</v>
       </c>
-      <c r="F286" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
-      <c r="A287" t="s">
+      <c r="D287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
         <v>561</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B288" t="s">
         <v>562</v>
       </c>
-      <c r="F287" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
-      <c r="A288" t="s">
+      <c r="D288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
         <v>563</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B289" t="s">
         <v>564</v>
       </c>
-      <c r="F288" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
-      <c r="A289" t="s">
+      <c r="D289" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
         <v>565</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B290" t="s">
         <v>566</v>
       </c>
-      <c r="F289" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
-      <c r="A290" t="s">
+      <c r="D290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
         <v>567</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B291" t="s">
         <v>568</v>
       </c>
-      <c r="F290" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291" t="s">
+      <c r="D291" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
         <v>569</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B292" t="s">
         <v>570</v>
       </c>
-      <c r="F291" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
-      <c r="A292" t="s">
+      <c r="D292" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
         <v>571</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B293" t="s">
         <v>572</v>
       </c>
-      <c r="F292" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
-      <c r="A293" t="s">
+      <c r="D293" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
         <v>573</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B294" t="s">
         <v>574</v>
       </c>
-      <c r="F293" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
-      <c r="A294" t="s">
+      <c r="D294" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
         <v>575</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B295" t="s">
         <v>576</v>
       </c>
-      <c r="F294" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295" t="s">
+      <c r="D295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
         <v>577</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B296" t="s">
         <v>578</v>
       </c>
-      <c r="F295" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
-      <c r="A296" t="s">
+      <c r="C296" t="s">
         <v>579</v>
       </c>
-      <c r="B296" t="s">
+      <c r="D296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
         <v>580</v>
       </c>
-      <c r="C296" t="s">
+      <c r="B297" t="s">
+        <v>578</v>
+      </c>
+      <c r="D297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
         <v>581</v>
       </c>
-      <c r="F296" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
-      <c r="A297" t="s">
+      <c r="B298" t="s">
         <v>582</v>
       </c>
-      <c r="B297" t="s">
-        <v>580</v>
-      </c>
-      <c r="F297" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
-      <c r="A298" t="s">
+      <c r="D298" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
         <v>583</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B299" t="s">
         <v>584</v>
       </c>
-      <c r="F298" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
-      <c r="A299" t="s">
+      <c r="D299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
         <v>585</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B300" t="s">
+        <v>396</v>
+      </c>
+      <c r="D300" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
         <v>586</v>
       </c>
-      <c r="F299" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
-      <c r="A300" t="s">
+      <c r="B301" t="s">
         <v>587</v>
       </c>
-      <c r="B300" t="s">
-        <v>398</v>
-      </c>
-      <c r="F300" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
-      <c r="A301" t="s">
+      <c r="D301" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
         <v>588</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B302" t="s">
+        <v>587</v>
+      </c>
+      <c r="D302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
         <v>589</v>
       </c>
-      <c r="F301" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
-      <c r="A302" t="s">
+      <c r="B303" t="s">
         <v>590</v>
       </c>
-      <c r="B302" t="s">
-        <v>589</v>
-      </c>
-      <c r="F302" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
-      <c r="A303" t="s">
+      <c r="D303" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
         <v>591</v>
       </c>
-      <c r="B303" t="s">
-        <v>592</v>
-      </c>
-      <c r="F303" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
-      <c r="A304" t="s">
-        <v>593</v>
-      </c>
       <c r="B304" t="s">
-        <v>589</v>
-      </c>
-      <c r="F304" t="s">
-        <v>8</v>
+        <v>587</v>
+      </c>
+      <c r="D304" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Currency.xlsx
+++ b/api/clv2/xlsx/en/Currency.xlsx
@@ -1411,7 +1411,7 @@
     <t>TOP</t>
   </si>
   <si>
-    <t>Pa’anga</t>
+    <t>Pa'anga</t>
   </si>
   <si>
     <t>TPE</t>
